--- a/docs/user-feedback.xlsx
+++ b/docs/user-feedback.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>Zaman damgası</t>
   </si>
@@ -122,6 +122,48 @@
   </si>
   <si>
     <t>UI/UX harika olsa da ana sayfada ufak bi yerde bütün ekranı kaplamıyor keşke full ekran olsa</t>
+  </si>
+  <si>
+    <t>Emir</t>
+  </si>
+  <si>
+    <t>manceflu@gmail.com</t>
+  </si>
+  <si>
+    <t>GBF4BV4IHSVRSGTVA3DYYTLM2X6BKY4DD7OWCVRTA3ZMPJRDGTZT6F7D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grup oluşturma, Harcama ekleme, Bakiye görüntüleme, Settle / Uzlaşma, Savings pool (birikim havuzu), Recurring expense (tekrarlayan ödeme), QR / link ile davet, Discord/Slack webhook, Social recovery (guardian), Diğer, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hepsi </t>
+  </si>
+  <si>
+    <t>Yok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mükemmel </t>
+  </si>
+  <si>
+    <t>Sıla</t>
+  </si>
+  <si>
+    <t>ser719549@gmail.com</t>
+  </si>
+  <si>
+    <t>GBHWCD2UA6SOWVWEA6DJVMCHXMRJ3HTH3VODXID3WVQ6L2SB4ZQ7P65L</t>
+  </si>
+  <si>
+    <t>Grup oluşturma, Diğer</t>
+  </si>
+  <si>
+    <t>hızlı ve kolayca öğrenilebiliyor</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>mobil uygulama olabilir</t>
   </si>
 </sst>
 </file>
@@ -259,7 +301,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M4" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M6" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Zaman damgası" id="1"/>
     <tableColumn name="1. Ad / Takma Ad" id="2"/>
@@ -653,6 +695,88 @@
         <v>19</v>
       </c>
     </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="5">
+        <v>46136.918360578704</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="5">
+        <v>46140.95280747685</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">
